--- a/eduservices/MOTEUR_ELASTICITE.xlsx
+++ b/eduservices/MOTEUR_ELASTICITE.xlsx
@@ -1026,10 +1026,9 @@
           <t>inscrits 2027</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  =  inscrits 2026  ×  ( budget marketing 2027 ÷ budget marketing 2026 ) ^ élasticité</t>
-        </is>
+      <c r="D13" s="10">
+        <f>"  =  inscrits 2026  ×  ( budget marketing 2027 ÷ budget marketing 2026 ) ^ "&amp;TEXT(Historique!$M$25,"0.00")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1190,6 +1189,13 @@
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>← le levier prix du cadrage V01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Sur chaque ligne campus :  inscrits 2027  =  inscrits 2026  ×  ( 1 + Δ budget marketing ) ^ élasticité du campus.  Les lignes marque et la ligne groupe sont les sommes de leurs campus.</t>
         </is>
       </c>
     </row>
